--- a/引脚.xlsx
+++ b/引脚.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuya\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\biyelunwen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB3D06B-A985-4ECE-9F52-CDD36BBCF518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A16ED-1D1B-4297-87D4-0E7028C09759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="660" windowWidth="25320" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>DHT11</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -160,6 +160,30 @@
   </si>
   <si>
     <t>PB11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SU-03T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE7,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE10，11，12，13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FAN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,10 +509,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,7 +529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -522,12 +546,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -544,7 +568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -561,7 +585,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -575,7 +599,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>24</v>
       </c>
@@ -583,7 +607,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>25</v>
       </c>
@@ -591,25 +615,46 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
         <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
